--- a/lab_10.xlsx
+++ b/lab_10.xlsx
@@ -339,6 +339,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -745,15 +749,15 @@
         <v>93</v>
       </c>
       <c r="J2" s="7">
-        <f>AVERAGE(E2:I2)</f>
+        <f t="shared" ref="J2:J16" si="0">AVERAGE(E2:I2)</f>
         <v>94</v>
       </c>
       <c r="K2" s="7">
-        <f>SUM(E2:I2)</f>
+        <f t="shared" ref="K2:K16" si="1">SUM(E2:I2)</f>
         <v>470</v>
       </c>
       <c r="L2" s="8">
-        <f>AVERAGE(E2:I2)/100</f>
+        <f t="shared" ref="L2:L16" si="2">AVERAGE(E2:I2)/100</f>
         <v>0.94</v>
       </c>
       <c r="M2" s="5">
@@ -793,15 +797,15 @@
         <v>94</v>
       </c>
       <c r="J3" s="7">
-        <f>AVERAGE(E3:I3)</f>
+        <f t="shared" si="0"/>
         <v>92</v>
       </c>
       <c r="K3" s="7">
-        <f>SUM(E3:I3)</f>
+        <f t="shared" si="1"/>
         <v>460</v>
       </c>
       <c r="L3" s="8">
-        <f>AVERAGE(E3:I3)/100</f>
+        <f t="shared" si="2"/>
         <v>0.92</v>
       </c>
       <c r="M3" s="5">
@@ -841,15 +845,15 @@
         <v>89</v>
       </c>
       <c r="J4" s="7">
-        <f>AVERAGE(E4:I4)</f>
+        <f t="shared" si="0"/>
         <v>90</v>
       </c>
       <c r="K4" s="7">
-        <f>SUM(E4:I4)</f>
+        <f t="shared" si="1"/>
         <v>450</v>
       </c>
       <c r="L4" s="8">
-        <f>AVERAGE(E4:I4)/100</f>
+        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="M4" s="5">
@@ -889,15 +893,15 @@
         <v>87</v>
       </c>
       <c r="J5" s="7">
-        <f>AVERAGE(E5:I5)</f>
+        <f t="shared" si="0"/>
         <v>88.4</v>
       </c>
       <c r="K5" s="7">
-        <f>SUM(E5:I5)</f>
+        <f t="shared" si="1"/>
         <v>442</v>
       </c>
       <c r="L5" s="8">
-        <f>AVERAGE(E5:I5)/100</f>
+        <f t="shared" si="2"/>
         <v>0.88400000000000001</v>
       </c>
       <c r="M5" s="5">
@@ -937,15 +941,15 @@
         <v>86</v>
       </c>
       <c r="J6" s="7">
-        <f>AVERAGE(E6:I6)</f>
+        <f t="shared" si="0"/>
         <v>87.2</v>
       </c>
       <c r="K6" s="7">
-        <f>SUM(E6:I6)</f>
+        <f t="shared" si="1"/>
         <v>436</v>
       </c>
       <c r="L6" s="8">
-        <f>AVERAGE(E6:I6)/100</f>
+        <f t="shared" si="2"/>
         <v>0.872</v>
       </c>
       <c r="M6" s="5">
@@ -985,15 +989,15 @@
         <v>84</v>
       </c>
       <c r="J7" s="7">
-        <f>AVERAGE(E7:I7)</f>
+        <f t="shared" si="0"/>
         <v>82.8</v>
       </c>
       <c r="K7" s="7">
-        <f>SUM(E7:I7)</f>
+        <f t="shared" si="1"/>
         <v>414</v>
       </c>
       <c r="L7" s="8">
-        <f>AVERAGE(E7:I7)/100</f>
+        <f t="shared" si="2"/>
         <v>0.82799999999999996</v>
       </c>
       <c r="M7" s="5">
@@ -1033,15 +1037,15 @@
         <v>80</v>
       </c>
       <c r="J8" s="7">
-        <f>AVERAGE(E8:I8)</f>
+        <f t="shared" si="0"/>
         <v>81.400000000000006</v>
       </c>
       <c r="K8" s="7">
-        <f>SUM(E8:I8)</f>
+        <f t="shared" si="1"/>
         <v>407</v>
       </c>
       <c r="L8" s="8">
-        <f>AVERAGE(E8:I8)/100</f>
+        <f t="shared" si="2"/>
         <v>0.81400000000000006</v>
       </c>
       <c r="M8" s="5">
@@ -1081,15 +1085,15 @@
         <v>72</v>
       </c>
       <c r="J9" s="7">
-        <f>AVERAGE(E9:I9)</f>
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
       <c r="K9" s="7">
-        <f>SUM(E9:I9)</f>
+        <f t="shared" si="1"/>
         <v>375</v>
       </c>
       <c r="L9" s="8">
-        <f>AVERAGE(E9:I9)/100</f>
+        <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
       <c r="M9" s="5">
@@ -1129,15 +1133,15 @@
         <v>71</v>
       </c>
       <c r="J10" s="7">
-        <f>AVERAGE(E10:I10)</f>
+        <f t="shared" si="0"/>
         <v>71</v>
       </c>
       <c r="K10" s="7">
-        <f>SUM(E10:I10)</f>
+        <f t="shared" si="1"/>
         <v>355</v>
       </c>
       <c r="L10" s="8">
-        <f>AVERAGE(E10:I10)/100</f>
+        <f t="shared" si="2"/>
         <v>0.71</v>
       </c>
       <c r="M10" s="5">
@@ -1177,15 +1181,15 @@
         <v>75</v>
       </c>
       <c r="J11" s="7">
-        <f>AVERAGE(E11:I11)</f>
+        <f t="shared" si="0"/>
         <v>70</v>
       </c>
       <c r="K11" s="7">
-        <f>SUM(E11:I11)</f>
+        <f t="shared" si="1"/>
         <v>350</v>
       </c>
       <c r="L11" s="8">
-        <f>AVERAGE(E11:I11)/100</f>
+        <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
       <c r="M11" s="5">
@@ -1225,15 +1229,15 @@
         <v>69</v>
       </c>
       <c r="J12" s="7">
-        <f>AVERAGE(E12:I12)</f>
+        <f t="shared" si="0"/>
         <v>68.8</v>
       </c>
       <c r="K12" s="7">
-        <f>SUM(E12:I12)</f>
+        <f t="shared" si="1"/>
         <v>344</v>
       </c>
       <c r="L12" s="8">
-        <f>AVERAGE(E12:I12)/100</f>
+        <f t="shared" si="2"/>
         <v>0.68799999999999994</v>
       </c>
       <c r="M12" s="5">
@@ -1273,15 +1277,15 @@
         <v>35</v>
       </c>
       <c r="J13" s="7">
-        <f>AVERAGE(E13:I13)</f>
+        <f t="shared" si="0"/>
         <v>68.2</v>
       </c>
       <c r="K13" s="7">
-        <f>SUM(E13:I13)</f>
+        <f t="shared" si="1"/>
         <v>341</v>
       </c>
       <c r="L13" s="8">
-        <f>AVERAGE(E13:I13)/100</f>
+        <f t="shared" si="2"/>
         <v>0.68200000000000005</v>
       </c>
       <c r="M13" s="5">
@@ -1321,15 +1325,15 @@
         <v>64</v>
       </c>
       <c r="J14" s="7">
-        <f>AVERAGE(E14:I14)</f>
+        <f t="shared" si="0"/>
         <v>61.8</v>
       </c>
       <c r="K14" s="7">
-        <f>SUM(E14:I14)</f>
+        <f t="shared" si="1"/>
         <v>309</v>
       </c>
       <c r="L14" s="8">
-        <f>AVERAGE(E14:I14)/100</f>
+        <f t="shared" si="2"/>
         <v>0.61799999999999999</v>
       </c>
       <c r="M14" s="5">
@@ -1369,15 +1373,15 @@
         <v>61</v>
       </c>
       <c r="J15" s="7">
-        <f>AVERAGE(E15:I15)</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="K15" s="7">
-        <f>SUM(E15:I15)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="L15" s="8">
-        <f>AVERAGE(E15:I15)/100</f>
+        <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
       <c r="M15" s="5">
@@ -1417,15 +1421,15 @@
         <v>65</v>
       </c>
       <c r="J16" s="7">
-        <f>AVERAGE(E16:I16)</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="K16" s="7">
-        <f>SUM(E16:I16)</f>
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
       <c r="L16" s="8">
-        <f>AVERAGE(E16:I16)/100</f>
+        <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
       <c r="M16" s="5">
